--- a/08_Project_Management/Task_Breakdown/Real_Time_Auction_Engine_Task_Breakdown_Sizing_Populated.xlsx
+++ b/08_Project_Management/Task_Breakdown/Real_Time_Auction_Engine_Task_Breakdown_Sizing_Populated.xlsx
@@ -922,7 +922,7 @@
         <v>The user (Bidder, AM, or Super Admin) is logged into the Auction Engine platform and opens the Overview Dashboard.</v>
       </c>
       <c r="F6" t="str">
-        <v>The system establishes an active WebSocket/live network connection.</v>
+        <v>The system establishes an active SSE/live stream network connection.</v>
       </c>
       <c r="G6" t="str" xml:space="preserve">
         <v xml:space="preserve">• The top header status pill component must dynamically render a green indicator showing "● Live • synced"._x000d_
@@ -3562,7 +3562,7 @@
         <v>The user is actively viewing the product detail page for "Vintage Rolex Submariner 1968".</v>
       </c>
       <c r="F13" t="str">
-        <v>The system detects a network failure or WebSocket disconnection (Connection lost).</v>
+        <v>The system detects a network failure or SSE disconnection (Connection lost).</v>
       </c>
       <c r="G13" t="str" xml:space="preserve">
         <v xml:space="preserve">• The top navigation bar displays a red badge: "Connection interrupted"._x000d_
@@ -3583,7 +3583,7 @@
         <v>The user clicks the "Retry now" button on the yellow warning banner.</v>
       </c>
       <c r="G14" t="str" xml:space="preserve">
-        <v xml:space="preserve">• The system attempts to re-initiate the WebSocket/API connection handshake._x000d_
+        <v xml:space="preserve">• The system attempts to re-initiate the SSE EventSource stream connection._x000d_
 • If successful, the warning banners disappear, and data fields (Current highest bid, Time remaining, Bid history) refresh to their latest real-time states.</v>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
         <v>The user (Bidder, AM, or Super Admin) is logged into the Auction Engine platform and opens the Overview Dashboard</v>
       </c>
       <c r="F6" t="str">
-        <v>The system establishes an active WebSocket/live network connection.</v>
+        <v>The system establishes an active SSE/live stream network connection.</v>
       </c>
       <c r="G6" t="str" xml:space="preserve">
         <v xml:space="preserve">• The top header status pill component must dynamically render a green indicator showing "● Live • synced"._x000d_
@@ -5365,7 +5365,7 @@
       </c>
       <c r="G11" t="str" xml:space="preserve">
         <v xml:space="preserve">The table must continuously print diagnostic metadata parameters containing:_x000d_
-• WebSocket channels: Total active connected clients (e.g., 1,254 connected)._x000d_
+• SSE client streams: Total active connected clients (e.g., 1,254 connected)._x000d_
 • Bid gateway p95: Instant latency tracker (e.g., 820ms)._x000d_
 • Event log: Throughput frequency speed tracking metrics (e.g., 120ms)._x000d_
 • Packet loss (%): Operational drop safety checker indicator (e.g., 0).</v>
@@ -9031,7 +9031,7 @@
         <v>Bid velocity reaches 10 bids in a single second and lot extension is set to 5 minutes</v>
       </c>
       <c r="G6" t="str">
-        <v>System extends the countdown by exactly 5 minutes and broadcasts the new end time via WebSocket</v>
+        <v>System extends the countdown by exactly 5 minutes and broadcasts the new end time via Server-Sent Events (SSE)</v>
       </c>
       <c r="H6" t="str">
         <v>Experienced in project</v>
